--- a/RSI Modular - copia/tabla_maestra_MERV.xlsx
+++ b/RSI Modular - copia/tabla_maestra_MERV.xlsx
@@ -548,25 +548,25 @@
         <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.46</v>
+        <v>-1.49</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.87</v>
+        <v>-1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.12</v>
+        <v>-3.22</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.5</v>
+        <v>-4.66</v>
       </c>
       <c r="I3" t="n">
-        <v>-10.25</v>
+        <v>-10.64</v>
       </c>
       <c r="J3" t="n">
-        <v>-23.62</v>
+        <v>-23.94</v>
       </c>
       <c r="K3" t="n">
-        <v>-37.9</v>
+        <v>-38.17</v>
       </c>
     </row>
     <row r="4">
@@ -604,10 +604,10 @@
         <v>14.25</v>
       </c>
       <c r="J4" t="n">
-        <v>31.88</v>
+        <v>31.52</v>
       </c>
       <c r="K4" t="n">
-        <v>45.34</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         <v>71</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="F5" t="n">
         <v>-2.05</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" t="n">
         <v>-0.84</v>
@@ -1220,25 +1220,25 @@
         <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="F3" t="n">
-        <v>46.2</v>
+        <v>44.7</v>
       </c>
       <c r="G3" t="n">
-        <v>46.2</v>
+        <v>44.7</v>
       </c>
       <c r="H3" t="n">
-        <v>25.6</v>
+        <v>23.7</v>
       </c>
       <c r="I3" t="n">
-        <v>25.6</v>
+        <v>23.7</v>
       </c>
       <c r="J3" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="K3" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="4">
@@ -1276,10 +1276,10 @@
         <v>73.5</v>
       </c>
       <c r="J4" t="n">
-        <v>75.8</v>
+        <v>76.5</v>
       </c>
       <c r="K4" t="n">
-        <v>83.3</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1302,7 +1302,7 @@
         <v>71</v>
       </c>
       <c r="E5" t="n">
-        <v>35.7</v>
+        <v>35.2</v>
       </c>
       <c r="F5" t="n">
         <v>38.6</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" t="n">
         <v>37.8</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
